--- a/resources/ai-for-your-business/files/aifyb-basics-saving-calculator.xlsx
+++ b/resources/ai-for-your-business/files/aifyb-basics-saving-calculator.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,11 +60,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -110,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,8 +145,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -552,7 +545,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
@@ -593,7 +585,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
@@ -604,7 +595,6 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
@@ -671,7 +661,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
@@ -683,7 +672,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -701,11 +689,10 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>The ~46-week year leaves room for holidays and quiet spells — change it to your own.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
+          <t>The ~46-week year leaves room for vacations and slow periods — change it to your own.</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
@@ -719,10 +706,6 @@
           <t>ePORTS — your ecom source. eports.global</t>
         </is>
       </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="18" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/ai-for-your-business/files/aifyb-basics-saving-calculator.xlsx
+++ b/resources/ai-for-your-business/files/aifyb-basics-saving-calculator.xlsx
@@ -703,7 +703,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
